--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260615.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260615.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>577,530,000</t>
+          <t>580,650,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>13.10%</t>
+          <t>13.44%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>658,070,000</t>
+          <t>651,470,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>12.29%</t>
+          <t>12.30%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>170,430,000</t>
+          <t>171,500,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>11.78%</t>
+          <t>11.52%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>880,807,000</t>
+          <t>872,007,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>11.07%</t>
+          <t>11.10%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>1,126,480,000</t>
+          <t>1,126,730,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>6.32%</t>
+          <t>6.46%</t>
         </is>
       </c>
     </row>
@@ -721,56 +721,56 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>33,990,000</t>
+          <t>33,650,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.96%</t>
+          <t>4.84%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>99,073,000</t>
+          <t>769,160,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.20%</t>
+          <t>4.02%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>765,470,000</t>
+          <t>98,073,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.91%</t>
+          <t>4.00%</t>
         </is>
       </c>
     </row>
@@ -792,271 +792,271 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.74%</t>
+          <t>3.70%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>202606TX</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>台指期</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>1,664</t>
+          <t>21,660,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.49%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>21,630,000</t>
+          <t>259,114,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>1.88%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>264,624,000</t>
+          <t>109,950,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>109,950,000</t>
+          <t>11,400,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>中租-KY</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>11,400,000</t>
+          <t>68,930,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>中租-KY</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>68,460,000</t>
+          <t>63,910,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>遠雄</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>72,239,000</t>
+          <t>203,760,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>5522</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>遠雄</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>63,910,000</t>
+          <t>72,239,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>203,680,000</t>
+          <t>25,430,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>25,950,000</t>
+          <t>36,460,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>國產</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>36,460,000</t>
+          <t>117,699,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>國產</t>
+          <t>正新</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>117,699,000</t>
+          <t>116,300,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
@@ -1073,34 +1073,34 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>11,948,000</t>
+          <t>12,008,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>正新</t>
+          <t>統一證</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>116,010,000</t>
+          <t>72,560,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.68%</t>
         </is>
       </c>
     </row>
@@ -1117,271 +1117,271 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>9,014,000</t>
+          <t>8,464,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.63%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>統一證</t>
+          <t>興富發</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>72,220,000</t>
+          <t>75,170,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.62%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>興富發</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>75,070,000</t>
+          <t>13,120,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>13,060,000</t>
+          <t>27,620,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>33,440,000</t>
+          <t>13,510,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>13,510,000</t>
+          <t>34,400,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>潤弘</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>27,490,000</t>
+          <t>14,080,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>34,730,000</t>
+          <t>38,943,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>潤弘</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>14,010,000</t>
+          <t>33,440,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>38,943,000</t>
+          <t>26,599,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>裕融</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>26,879,000</t>
+          <t>29,700,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>裕融</t>
+          <t>義隆</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>29,560,000</t>
+          <t>15,230,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>義隆</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>15,540,000</t>
+          <t>41,040,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,44 +1393,44 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>40,840,000</t>
+          <t>7,890,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>202606TX</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>台指期</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>7,830,000</t>
+          <t>244</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>27,116,000</t>
+          <t>27,986,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>20,040,000</t>
+          <t>20,280,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>9,479,146,629</t>
+          <t>14,835,187,267</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr"/>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>2,147,325,717</t>
+          <t>2,603,947,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr"/>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>2,292,337,642</t>
+          <t>1,768,378,278</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr"/>
